--- a/event_registration_forms/023_sweet_16_celebration_survey--event_registration_forms.xlsx
+++ b/event_registration_forms/023_sweet_16_celebration_survey--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>event guest info</t>
+          <t>Event Guest Info Repeat</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>party preferences</t>
+          <t>Party Preferences Repeat</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>guest diet</t>
+          <t>Guest Diet Repeat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email Repeat</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>phone number</t>
+          <t>Phone Number Repeat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>event date</t>
+          <t>Event Date Repeat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>event time</t>
+          <t>Event Time Repeat</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments Repeat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1199,29 +1199,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Games</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>party_preferences_choices</t>
+          <t>guest_diet_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>vegetarian</t>
+          <t>non-vegetarian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Non-Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>non-vegetarian</t>
+          <t>pescetarian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Non-Vegetarian</t>
+          <t>Pescetarian</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pescetarian</t>
+          <t>ประกother'</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pescetarian</t>
+          <t>ประกOther'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>guest_diet_choices</t>
+          <t>party_preferences_repeat_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ประกother'</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ประกOther'</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dance</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dance</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>music</t>
+          <t>games</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Games</t>
         </is>
       </c>
     </row>
@@ -1352,46 +1352,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Games</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>party_preferences_repeat_choices</t>
+          <t>guest_diet_repeat_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Games</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>party_preferences_repeat_choices</t>
+          <t>guest_diet_repeat_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>non-vegetarian</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>vegetarian</t>
+          <t>pescetarian</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Pescetarian</t>
         </is>
       </c>
     </row>
@@ -1420,46 +1420,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>non-vegetarian</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Non-Vegetarian</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>guest_diet_repeat_choices</t>
+          <t>guest_attendance_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pescetarian</t>
+          <t>attend</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pescetarian</t>
+          <t>Attend</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>guest_diet_repeat_choices</t>
+          <t>guest_attendance_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>not_attend</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Not Attend</t>
         </is>
       </c>
     </row>
@@ -1471,44 +1471,10 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>attend</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>Attend</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>guest_attendance_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>not_attend</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Not Attend</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>guest_attendance_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
